--- a/reference/영상제작비견적서2.xlsx
+++ b/reference/영상제작비견적서2.xlsx
@@ -1,708 +1,287 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CHEIL\Desktop\AI TF - pioneer\reference\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213661E7-CC98-4383-AD82-E925C7222E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="984" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="자동차보험" sheetId="63" r:id="rId1"/>
-    <sheet name="운전자보험" sheetId="65" r:id="rId2"/>
+    <sheet name="자동차보험" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="운전자보험" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_1" localSheetId="1">[1]I一般比!#REF!</definedName>
-    <definedName name="_1" localSheetId="0">[1]I一般比!#REF!</definedName>
     <definedName name="_1">[1]I一般比!#REF!</definedName>
-    <definedName name="_2" localSheetId="1">[1]I一般比!#REF!</definedName>
-    <definedName name="_2" localSheetId="0">[1]I一般比!#REF!</definedName>
     <definedName name="_2">[1]I一般比!#REF!</definedName>
     <definedName name="_3">#N/A</definedName>
-    <definedName name="_4" localSheetId="1">[1]I一般比!#REF!</definedName>
-    <definedName name="_4" localSheetId="0">[1]I一般比!#REF!</definedName>
     <definedName name="_4">[1]I一般比!#REF!</definedName>
     <definedName name="\0">#N/A</definedName>
     <definedName name="\a">#N/A</definedName>
-    <definedName name="\g" localSheetId="1">'[1]N賃率-職'!#REF!</definedName>
-    <definedName name="\g" localSheetId="0">'[1]N賃率-職'!#REF!</definedName>
     <definedName name="\g">'[1]N賃率-職'!#REF!</definedName>
     <definedName name="\x">#N/A</definedName>
     <definedName name="\z">#N/A</definedName>
+    <definedName name="dddd">[2]I一般比!#REF!</definedName>
+    <definedName name="기ㅏㅓㅣㅏㅓㅏㅣㅓ">[1]I一般比!#REF!</definedName>
+    <definedName name="ㄴㄴ">[1]I一般比!#REF!</definedName>
+    <definedName name="ㄷㄱㄷ">'[1]N賃率-職'!#REF!</definedName>
+    <definedName name="ㅇㅇ">[1]I一般比!#REF!</definedName>
+    <definedName name="_1" localSheetId="0">[1]I一般比!#REF!</definedName>
+    <definedName name="_2" localSheetId="0">[1]I一般比!#REF!</definedName>
+    <definedName name="_4" localSheetId="0">[1]I一般比!#REF!</definedName>
+    <definedName name="\g" localSheetId="0">'[1]N賃率-職'!#REF!</definedName>
+    <definedName name="dddd" localSheetId="0">[2]I一般比!#REF!</definedName>
+    <definedName name="기ㅏㅓㅣㅏㅓㅏㅣㅓ" localSheetId="0">[1]I一般比!#REF!</definedName>
+    <definedName name="ㄴㄴ" localSheetId="0">[1]I一般比!#REF!</definedName>
+    <definedName name="ㄷㄱㄷ" localSheetId="0">'[1]N賃率-職'!#REF!</definedName>
+    <definedName name="ㅇㅇ" localSheetId="0">[1]I一般比!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'자동차보험'!$A$1:$L$34</definedName>
+    <definedName name="_1" localSheetId="1">[1]I一般比!#REF!</definedName>
+    <definedName name="_2" localSheetId="1">[1]I一般比!#REF!</definedName>
+    <definedName name="_4" localSheetId="1">[1]I一般比!#REF!</definedName>
+    <definedName name="\g" localSheetId="1">'[1]N賃率-職'!#REF!</definedName>
     <definedName name="dddd" localSheetId="1">[2]I一般比!#REF!</definedName>
-    <definedName name="dddd" localSheetId="0">[2]I一般比!#REF!</definedName>
-    <definedName name="dddd">[2]I一般比!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">운전자보험!$A$1:$L$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">자동차보험!$A$1:$L$34</definedName>
     <definedName name="기ㅏㅓㅣㅏㅓㅏㅣㅓ" localSheetId="1">[1]I一般比!#REF!</definedName>
-    <definedName name="기ㅏㅓㅣㅏㅓㅏㅣㅓ" localSheetId="0">[1]I一般比!#REF!</definedName>
-    <definedName name="기ㅏㅓㅣㅏㅓㅏㅣㅓ">[1]I一般比!#REF!</definedName>
     <definedName name="ㄴㄴ" localSheetId="1">[1]I一般比!#REF!</definedName>
-    <definedName name="ㄴㄴ" localSheetId="0">[1]I一般比!#REF!</definedName>
-    <definedName name="ㄴㄴ">[1]I一般比!#REF!</definedName>
     <definedName name="ㄷㄱㄷ" localSheetId="1">'[1]N賃率-職'!#REF!</definedName>
-    <definedName name="ㄷㄱㄷ" localSheetId="0">'[1]N賃率-職'!#REF!</definedName>
-    <definedName name="ㄷㄱㄷ">'[1]N賃率-職'!#REF!</definedName>
     <definedName name="ㅇㅇ" localSheetId="1">[1]I一般比!#REF!</definedName>
-    <definedName name="ㅇㅇ" localSheetId="0">[1]I一般比!#REF!</definedName>
-    <definedName name="ㅇㅇ">[1]I一般比!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'운전자보험'!$A$1:$L$40</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="100">
-  <si>
-    <t>세부내용</t>
-  </si>
-  <si>
-    <t>협력회사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제 작 항 목 </t>
-  </si>
-  <si>
-    <t>외주항목계 (B)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>공급자</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIENT </t>
-  </si>
-  <si>
-    <t>회사명</t>
-  </si>
-  <si>
-    <t>대표이사</t>
-  </si>
-  <si>
-    <t>유 정 근</t>
-  </si>
-  <si>
-    <t>사업자등록번호</t>
-  </si>
-  <si>
-    <t>202-81-45960</t>
-  </si>
-  <si>
-    <t>견적금액</t>
-  </si>
-  <si>
-    <t>사업장주소</t>
-  </si>
-  <si>
-    <t>서울특별시 용산구 이태원로 222 (한남동)</t>
-  </si>
-  <si>
-    <t>담당자/연락처</t>
-  </si>
-  <si>
-    <t>아래와 같이
-견적 합니다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>담당자</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>수량</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>정가항목</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>정가항목 (A)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>기 획 료</t>
-  </si>
-  <si>
-    <t>COPY료</t>
-  </si>
-  <si>
-    <t>Creative Work료</t>
-  </si>
-  <si>
-    <t>Direction료</t>
-  </si>
-  <si>
-    <t>자료조사비</t>
-  </si>
-  <si>
-    <t>청구금액</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로젝트 매니저료</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>합계금액</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Job Name</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Job</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">CW : </t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">AD : </t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>On-Air :</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>촬영일 :</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>협력업체 :</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CD(제작팀) :</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Job :</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Job Name :</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>제일기획
-(작품당)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Post프로덕션</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>라이브러리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>폰트</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>이미지</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>저작권
-라이선스</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>[CM영상제작 표준 견적서 ]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>제작비 명세서</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>(주)제일기획</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>매체 :</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>기타</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>대행수수료 (C)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (B)항목 * 17.65%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (A)+(B)+(C)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>녹음실</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>오디오PD</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>이재환
-김형운
-조영찬
-권두인</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>제작</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>공급받는자</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로덕션</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CF 프로덕션</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">AE : </t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>PM :</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>편집</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>NTC</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>성우</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>프리랜서</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>제일기획 정가항목 미적용</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (VAT 포함)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (B)항목 * 17.65%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>우경훈 프로
-권두인 프로
-조영찬 프로</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>박현정</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>오창규 등</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>박지환 등</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>이재환, 우경훈, 권두인 조영찬</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>김미애</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1차 사전견적</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 사전견적</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>PD</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Producer</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>크림치즈필름</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>오드아이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>포나인</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>합성</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>킹콩</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>레솔트뮤지끄</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>데이브레이크_넌언제나</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>15" x 2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>30", 15" 등</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>콘티</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>콘티/일러스트</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>투디</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>제일기획 대행수수료 조정 (17.65% → 10%)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동건</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>데이브레이크_들었다놨다</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>조정견적</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>사전견적</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1차 조정견적</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>최종견적</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="24" formatCode="\$#,##0_);[Red]\(\$#,##0\)"/>
-    <numFmt numFmtId="176" formatCode="#,##0_ "/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="&quot;₩&quot;#,##0"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="182" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="183" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="185" formatCode="0.000%"/>
-    <numFmt numFmtId="186" formatCode="&quot;₩&quot;#,##0.0"/>
-    <numFmt numFmtId="187" formatCode="&quot;₩&quot;\ #,##0\ &quot;원&quot;\(\V\A\T&quot;별&quot;&quot;도&quot;\)"/>
-    <numFmt numFmtId="188" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="12">
+    <numFmt numFmtId="164" formatCode="\$#,##0_);[Red]\(\$#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.000%"/>
+    <numFmt numFmtId="168" formatCode="&quot;₩&quot;#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0_ "/>
+    <numFmt numFmtId="170" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+    <numFmt numFmtId="171" formatCode="&quot;₩&quot;\ #,##0\ &quot;원&quot;\(\V\A\T&quot;별&quot;&quot;도&quot;\)"/>
+    <numFmt numFmtId="172" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="173" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="174" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="30">
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <name val="돋움"/>
       <family val="3"/>
-      <charset val="129"/>
+      <sz val="8"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="돋움"/>
       <family val="3"/>
-      <charset val="129"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="돋움"/>
-      <family val="3"/>
+      <name val="ARIAL"/>
+      <family val="2"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="돋움"/>
-      <family val="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="ARIAL"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="굴림체"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <sz val="13"/>
+      <u val="single"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="굴림체"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="13"/>
       <name val="굴림체"/>
+      <charset val="129"/>
       <family val="3"/>
-      <charset val="129"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="바탕체"/>
+      <charset val="129"/>
+      <family val="1"/>
       <sz val="12"/>
-      <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="바탕체"/>
-      <family val="1"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FFFF0000"/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="12"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="12"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="24"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -738,12 +317,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="60">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1480,69 +1059,210 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="85">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="3" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="9" fontId="14" fillId="3" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="3" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="9" fontId="14" fillId="3" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="14" fillId="3" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="175" fontId="14" fillId="3" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="184" fontId="14" fillId="3" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="175" fontId="14" fillId="3" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
@@ -1554,907 +1274,948 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="24" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="59">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="59" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="173" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="156">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="229">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="24" fontId="20" fillId="2" borderId="4" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="0" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" xfId="39" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" xfId="39" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="186" fontId="17" fillId="0" borderId="0" xfId="39" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="39" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="0" xfId="39" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="24" fontId="19" fillId="6" borderId="4" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="0" borderId="0" xfId="39" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="6" borderId="31" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="20" fillId="6" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="20" fillId="6" borderId="32" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="46" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="0" borderId="47" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="0" borderId="48" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="2" borderId="46" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="20" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="48" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="6" borderId="46" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="20" fillId="6" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="15" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="57" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="57" xfId="39" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="57" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="57" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="58" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="26" fillId="0" borderId="0" xfId="39" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="6" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="5" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="4" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="24" fontId="27" fillId="7" borderId="4" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="27" fillId="7" borderId="46" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="27" fillId="7" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" xfId="38" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="4" borderId="6" xfId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="29">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" xfId="15" applyFont="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="188" fontId="20" fillId="2" borderId="57" xfId="39" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="20" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="56" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="8" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="24" fontId="20" fillId="5" borderId="8" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="8" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="5" borderId="49" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="20" fillId="5" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="6" borderId="31" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="25" fillId="6" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="6" borderId="32" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="25" fillId="6" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="2" borderId="46" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="25" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="28" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="22" fillId="6" borderId="31" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="22" fillId="6" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="8" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="28" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="22" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="26" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="45" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="54" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="50" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="51" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="26" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="28" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="26" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="18" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="27" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="17" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="52" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="53" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="55" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="20" xfId="38" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="25" xfId="38" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="38" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="37" xfId="38" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="38" xfId="38" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="41" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="59" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="19" fillId="7" borderId="14" xfId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="19" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="19" fillId="7" borderId="29" xfId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="19" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="55" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="38" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="20" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="25" fillId="6" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="25" fillId="6" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="20" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="29">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="25" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="5" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="6" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="7" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="19" fillId="7" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="22" fillId="6" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="6" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="85">
-    <cellStyle name="Comma [0]_laroux" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Comma_laroux" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Currency [0]_laroux" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Currency_laroux" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Header1" xfId="64" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Header2" xfId="65" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal_Certs Q2" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="title [1]" xfId="6" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="title [1] 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="title [2]" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="title [2] 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]_laroux" xfId="1"/>
+    <cellStyle name="Comma_laroux" xfId="2"/>
+    <cellStyle name="Currency [0]_laroux" xfId="3"/>
+    <cellStyle name="Currency_laroux" xfId="4"/>
+    <cellStyle name="Normal_Certs Q2" xfId="5"/>
+    <cellStyle name="title [1]" xfId="6"/>
+    <cellStyle name="title [1] 2" xfId="7"/>
+    <cellStyle name="title [2]" xfId="8"/>
+    <cellStyle name="title [2] 2" xfId="9"/>
     <cellStyle name="백분율" xfId="10" builtinId="5"/>
-    <cellStyle name="백분율 [0]" xfId="11" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="백분율 [0] 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="백분율 [2]" xfId="13" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="백분율 [2] 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="백분율 [0]" xfId="11"/>
+    <cellStyle name="백분율 [0] 2" xfId="12"/>
+    <cellStyle name="백분율 [2]" xfId="13"/>
+    <cellStyle name="백분율 [2] 2" xfId="14"/>
     <cellStyle name="쉼표 [0]" xfId="15" builtinId="6"/>
-    <cellStyle name="쉼표 [0] 10" xfId="60" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="쉼표 [0] 11" xfId="84" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="쉼표 [0] 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="쉼표 [0] 2 15" xfId="17" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="쉼표 [0] 2 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="쉼표 [0] 2 2 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="쉼표 [0] 2 2 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="쉼표 [0] 2 3" xfId="20" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="쉼표 [0] 2 4" xfId="21" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="쉼표 [0] 2 5" xfId="56" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="쉼표 [0] 3" xfId="22" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="쉼표 [0] 3 2" xfId="71" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="쉼표 [0] 3 3" xfId="68" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="쉼표 [0] 4" xfId="23" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="쉼표 [0] 4 2" xfId="77" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="쉼표 [0] 4 3" xfId="74" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="쉼표 [0] 5" xfId="24" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="쉼표 [0] 5 2" xfId="78" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="쉼표 [0] 5 3" xfId="76" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="쉼표 [0] 6" xfId="25" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="쉼표 [0] 6 2" xfId="63" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="쉼표 [0] 7" xfId="53" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="쉼표 [0] 8" xfId="55" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="쉼표 [0] 9" xfId="57" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="콤마 [0]_1안" xfId="26" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="콤마 [2]" xfId="27" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="콤마 [2] 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="콤마_6월실적" xfId="66" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 - Styl1" xfId="29" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="표준 10" xfId="30" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="표준 11" xfId="31" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="표준 12" xfId="32" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="표준 13" xfId="33" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="표준 14" xfId="34" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="표준 15" xfId="35" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="표준 16" xfId="36" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="표준 17" xfId="37" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="표준 18" xfId="38" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="표준 19" xfId="52" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="표준 19 2" xfId="59" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="표준 2" xfId="39" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="표준 2 10 3" xfId="40" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="표준 2 2" xfId="41" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="표준 2 2 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="표준 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="표준 20" xfId="54" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="표준 21" xfId="58" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="표준 22" xfId="61" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="표준 3" xfId="44" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="표준 3 2" xfId="45" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="표준 3 2 2" xfId="79" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="표준 3 2 3" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="표준 4" xfId="46" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="표준 4 2" xfId="80" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="표준 4 3" xfId="67" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="표준 5" xfId="47" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="표준 5 2" xfId="70" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="표준 6" xfId="48" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="표준 6 2" xfId="81" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="표준 7" xfId="49" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="표준 7 2" xfId="82" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="표준 7 3" xfId="73" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="표준 8" xfId="50" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="표준 8 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="표준 8 3" xfId="75" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="표준 9" xfId="51" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="표준 9 2" xfId="62" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="쉼표 [0] 2" xfId="16"/>
+    <cellStyle name="쉼표 [0] 2 15" xfId="17"/>
+    <cellStyle name="쉼표 [0] 2 2" xfId="18"/>
+    <cellStyle name="쉼표 [0] 2 2 2" xfId="19"/>
+    <cellStyle name="쉼표 [0] 2 3" xfId="20"/>
+    <cellStyle name="쉼표 [0] 2 4" xfId="21"/>
+    <cellStyle name="쉼표 [0] 3" xfId="22"/>
+    <cellStyle name="쉼표 [0] 4" xfId="23"/>
+    <cellStyle name="쉼표 [0] 5" xfId="24"/>
+    <cellStyle name="쉼표 [0] 6" xfId="25"/>
+    <cellStyle name="콤마 [0]_1안" xfId="26"/>
+    <cellStyle name="콤마 [2]" xfId="27"/>
+    <cellStyle name="콤마 [2] 2" xfId="28"/>
+    <cellStyle name="표준 - Styl1" xfId="29"/>
+    <cellStyle name="표준 10" xfId="30"/>
+    <cellStyle name="표준 11" xfId="31"/>
+    <cellStyle name="표준 12" xfId="32"/>
+    <cellStyle name="표준 13" xfId="33"/>
+    <cellStyle name="표준 14" xfId="34"/>
+    <cellStyle name="표준 15" xfId="35"/>
+    <cellStyle name="표준 16" xfId="36"/>
+    <cellStyle name="표준 17" xfId="37"/>
+    <cellStyle name="표준 18" xfId="38"/>
+    <cellStyle name="표준 2" xfId="39"/>
+    <cellStyle name="표준 2 10 3" xfId="40"/>
+    <cellStyle name="표준 2 2" xfId="41"/>
+    <cellStyle name="표준 2 2 2" xfId="42"/>
+    <cellStyle name="표준 2 3" xfId="43"/>
+    <cellStyle name="표준 3" xfId="44"/>
+    <cellStyle name="표준 3 2" xfId="45"/>
+    <cellStyle name="표준 4" xfId="46"/>
+    <cellStyle name="표준 5" xfId="47"/>
+    <cellStyle name="표준 6" xfId="48"/>
+    <cellStyle name="표준 7" xfId="49"/>
+    <cellStyle name="표준 8" xfId="50"/>
+    <cellStyle name="표준 9" xfId="51"/>
+    <cellStyle name="표준 19" xfId="52"/>
+    <cellStyle name="쉼표 [0] 7" xfId="53"/>
+    <cellStyle name="표준 20" xfId="54"/>
+    <cellStyle name="쉼표 [0] 8" xfId="55"/>
+    <cellStyle name="쉼표 [0] 2 5" xfId="56"/>
+    <cellStyle name="쉼표 [0] 9" xfId="57"/>
+    <cellStyle name="표준 21" xfId="58"/>
+    <cellStyle name="표준 19 2" xfId="59"/>
+    <cellStyle name="쉼표 [0] 10" xfId="60"/>
+    <cellStyle name="표준 22" xfId="61"/>
+    <cellStyle name="표준 9 2" xfId="62"/>
+    <cellStyle name="쉼표 [0] 6 2" xfId="63"/>
+    <cellStyle name="Header1" xfId="64"/>
+    <cellStyle name="Header2" xfId="65"/>
+    <cellStyle name="콤마_6월실적" xfId="66"/>
+    <cellStyle name="표준 4 3" xfId="67"/>
+    <cellStyle name="쉼표 [0] 3 3" xfId="68"/>
+    <cellStyle name="표준 3 2 3" xfId="69"/>
+    <cellStyle name="표준 5 2" xfId="70"/>
+    <cellStyle name="쉼표 [0] 3 2" xfId="71"/>
+    <cellStyle name="쉼표 [0] 2 2 3" xfId="72"/>
+    <cellStyle name="표준 7 3" xfId="73"/>
+    <cellStyle name="쉼표 [0] 4 3" xfId="74"/>
+    <cellStyle name="표준 8 3" xfId="75"/>
+    <cellStyle name="쉼표 [0] 5 3" xfId="76"/>
+    <cellStyle name="쉼표 [0] 4 2" xfId="77"/>
+    <cellStyle name="쉼표 [0] 5 2" xfId="78"/>
+    <cellStyle name="표준 3 2 2" xfId="79"/>
+    <cellStyle name="표준 4 2" xfId="80"/>
+    <cellStyle name="표준 6 2" xfId="81"/>
+    <cellStyle name="표준 7 2" xfId="82"/>
+    <cellStyle name="표준 8 2" xfId="83"/>
+    <cellStyle name="쉼표 [0] 11" xfId="84"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFCCFFCC"/>
-      <color rgb="FF0000FF"/>
-      <color rgb="FFC0C0C0"/>
-      <color rgb="FF00CC99"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>15973</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>178137</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>102564</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>481205</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>15973</colOff>
+      <row>0</row>
+      <rowOff>178137</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>102564</colOff>
+      <row>0</row>
+      <rowOff>481205</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="그림 1"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      </blipFill>
+      <spPr bwMode="auto">
         <a:xfrm>
           <a:off x="101698" y="178137"/>
           <a:ext cx="1039091" cy="303068"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1025" name="AutoShape 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="14887575" y="7696200"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>82648</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>206712</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>83514</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>509780</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>82648</colOff>
+      <row>0</row>
+      <rowOff>206712</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>83514</colOff>
+      <row>0</row>
+      <rowOff>509780</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="그림 1"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      </blipFill>
+      <spPr bwMode="auto">
         <a:xfrm>
           <a:off x="82648" y="206712"/>
           <a:ext cx="1039091" cy="303068"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="A製總"/>
       <sheetName val="I一般比"/>
@@ -3666,8 +3427,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="A製總"/>
       <sheetName val="I一般比"/>
@@ -5294,1793 +5055,2179 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Q46"/>
-  <sheetFormatPr defaultColWidth="7.88671875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q46"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="7.88671875" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="5" customWidth="1"/>
-    <col min="9" max="10" width="12.88671875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="32.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="0.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="7.88671875" style="1"/>
+    <col width="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="11.109375" customWidth="1" style="2" min="2" max="2"/>
+    <col width="11.109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="20.44140625" customWidth="1" style="4" min="4" max="4"/>
+    <col width="12.33203125" customWidth="1" style="5" min="5" max="5"/>
+    <col width="11.109375" customWidth="1" style="2" min="6" max="6"/>
+    <col width="8.44140625" customWidth="1" style="2" min="7" max="7"/>
+    <col width="12.44140625" customWidth="1" style="5" min="8" max="8"/>
+    <col width="12.88671875" customWidth="1" style="5" min="9" max="10"/>
+    <col width="32.88671875" bestFit="1" customWidth="1" style="5" min="11" max="11"/>
+    <col width="0.88671875" customWidth="1" style="1" min="12" max="12"/>
+    <col width="15.33203125" customWidth="1" style="1" min="13" max="13"/>
+    <col width="7.88671875" customWidth="1" style="1" min="14" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="127" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-    </row>
-    <row r="2" spans="2:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-    </row>
-    <row r="4" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="49"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-    </row>
-    <row r="5" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" s="51"/>
-    </row>
-    <row r="6" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" s="49"/>
-    </row>
-    <row r="7" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-    </row>
-    <row r="8" spans="2:11" s="8" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="126"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="126"/>
-      <c r="H8" s="126"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="126"/>
-      <c r="K8" s="126"/>
-    </row>
-    <row r="9" spans="2:11" s="17" customFormat="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="93" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="113" t="s">
+    <row r="1" ht="48" customHeight="1" s="156" thickBot="1">
+      <c r="B1" s="127" t="inlineStr">
+        <is>
+          <t>제작비 명세서</t>
+        </is>
+      </c>
+      <c r="C1" s="157" t="n"/>
+      <c r="D1" s="157" t="n"/>
+      <c r="E1" s="157" t="n"/>
+      <c r="F1" s="157" t="n"/>
+      <c r="G1" s="157" t="n"/>
+      <c r="H1" s="157" t="n"/>
+      <c r="I1" s="157" t="n"/>
+      <c r="J1" s="157" t="n"/>
+      <c r="K1" s="157" t="n"/>
+    </row>
+    <row r="2" ht="12" customHeight="1" s="156">
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Job :</t>
+        </is>
+      </c>
+      <c r="C3" s="47" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="47" t="n"/>
+      <c r="F3" s="48" t="n"/>
+      <c r="G3" s="48" t="n"/>
+      <c r="H3" s="47" t="n"/>
+      <c r="I3" s="47" t="n"/>
+      <c r="J3" s="47" t="n"/>
+      <c r="K3" s="47" t="n"/>
+    </row>
+    <row r="4" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Job Name :</t>
+        </is>
+      </c>
+      <c r="C4" s="49" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="49" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>매체 :</t>
+        </is>
+      </c>
+      <c r="G4" s="49" t="inlineStr">
+        <is>
+          <t>15" x 2</t>
+        </is>
+      </c>
+      <c r="H4" s="49" t="n"/>
+      <c r="I4" s="50" t="n"/>
+      <c r="J4" s="50" t="n"/>
+      <c r="K4" s="50" t="n"/>
+    </row>
+    <row r="5" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>CD(제작팀) :</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>박현정</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD : </t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
+        <is>
+          <t>오창규 등</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CW : </t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>박지환 등</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE : </t>
+        </is>
+      </c>
+      <c r="I5" s="51" t="inlineStr">
+        <is>
+          <t>이재환, 우경훈, 권두인 조영찬</t>
+        </is>
+      </c>
+      <c r="J5" s="51" t="inlineStr">
+        <is>
+          <t>이재환, 우경훈, 권두인 조영찬</t>
+        </is>
+      </c>
+      <c r="K5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>협력업체 :</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="50" t="n"/>
+      <c r="G6" s="50" t="n"/>
+      <c r="H6" s="95" t="inlineStr">
+        <is>
+          <t>PM :</t>
+        </is>
+      </c>
+      <c r="I6" s="49" t="inlineStr">
+        <is>
+          <t>김미애</t>
+        </is>
+      </c>
+      <c r="J6" s="49" t="inlineStr">
+        <is>
+          <t>김미애</t>
+        </is>
+      </c>
+      <c r="K6" s="49" t="n"/>
+    </row>
+    <row r="7" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>촬영일 :</t>
+        </is>
+      </c>
+      <c r="C7" s="158" t="n"/>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>On-Air :</t>
+        </is>
+      </c>
+      <c r="E7" s="57" t="n"/>
+      <c r="F7" s="58" t="n"/>
+      <c r="G7" s="58" t="n"/>
+      <c r="H7" s="59" t="n"/>
+      <c r="I7" s="59" t="n"/>
+      <c r="J7" s="59" t="n"/>
+      <c r="K7" s="59" t="n"/>
+    </row>
+    <row r="8" ht="13.5" customFormat="1" customHeight="1" s="8" thickBot="1">
+      <c r="B8" s="126" t="n"/>
+      <c r="C8" s="159" t="n"/>
+      <c r="D8" s="159" t="n"/>
+      <c r="E8" s="159" t="n"/>
+      <c r="F8" s="159" t="n"/>
+      <c r="G8" s="159" t="n"/>
+      <c r="H8" s="159" t="n"/>
+      <c r="I8" s="159" t="n"/>
+      <c r="J8" s="159" t="n"/>
+      <c r="K8" s="159" t="n"/>
+    </row>
+    <row r="9" customFormat="1" s="17" thickBot="1">
+      <c r="B9" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제 작 항 목 </t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>세부내용</t>
+        </is>
+      </c>
+      <c r="D9" s="160" t="n"/>
+      <c r="E9" s="113" t="inlineStr">
+        <is>
+          <t>협력회사</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="G9" s="114" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="H9" s="41" t="inlineStr">
+        <is>
+          <t>사전견적</t>
+        </is>
+      </c>
+      <c r="I9" s="41" t="inlineStr">
+        <is>
+          <t>1차 조정견적</t>
+        </is>
+      </c>
+      <c r="J9" s="41" t="inlineStr">
+        <is>
+          <t>최종견적</t>
+        </is>
+      </c>
+      <c r="K9" s="70" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B10" s="104" t="inlineStr">
+        <is>
+          <t>정가항목</t>
+        </is>
+      </c>
+      <c r="C10" s="161" t="inlineStr">
+        <is>
+          <t>기 획 료</t>
+        </is>
+      </c>
+      <c r="D10" s="162" t="n"/>
+      <c r="E10" s="163" t="inlineStr">
+        <is>
+          <t>광고대행사
+(작품당)</t>
+        </is>
+      </c>
+      <c r="F10" s="164" t="inlineStr">
+        <is>
+          <t>이재환
+김형운
+조영찬
+권두인</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="165" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I10" s="166" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="114"/>
-      <c r="E9" s="92" t="s">
+      <c r="J10" s="166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="167" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B11" s="168" t="n"/>
+      <c r="C11" s="169" t="inlineStr">
+        <is>
+          <t>COPY료</t>
+        </is>
+      </c>
+      <c r="D11" s="170" t="n"/>
+      <c r="E11" s="171" t="n"/>
+      <c r="F11" s="171" t="n"/>
+      <c r="G11" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" s="70" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="104" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="115" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="116"/>
-      <c r="E10" s="117" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="117" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="18">
+      <c r="H11" s="172" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I11" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B12" s="168" t="n"/>
+      <c r="C12" s="169" t="inlineStr">
+        <is>
+          <t>Creative Work료</t>
+        </is>
+      </c>
+      <c r="D12" s="170" t="n"/>
+      <c r="E12" s="171" t="n"/>
+      <c r="F12" s="171" t="n"/>
+      <c r="G12" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="42">
-        <v>3000000</v>
-      </c>
-      <c r="I10" s="88">
+      <c r="H12" s="172" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I12" s="173" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="88">
+      <c r="J12" s="173" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="107"/>
-    </row>
-    <row r="11" spans="2:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="105"/>
-      <c r="C11" s="122" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="123"/>
-      <c r="E11" s="118"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="20">
+    </row>
+    <row r="13" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B13" s="168" t="n"/>
+      <c r="C13" s="169" t="inlineStr">
+        <is>
+          <t>Direction료</t>
+        </is>
+      </c>
+      <c r="D13" s="170" t="n"/>
+      <c r="E13" s="171" t="n"/>
+      <c r="F13" s="171" t="n"/>
+      <c r="G13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H13" s="165" t="n">
         <v>2000000</v>
       </c>
-      <c r="I11" s="89">
+      <c r="I13" s="166" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="89">
+      <c r="J13" s="166" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="108"/>
-    </row>
-    <row r="12" spans="2:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="105"/>
-      <c r="C12" s="122" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="123"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="21">
+    </row>
+    <row r="14" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B14" s="168" t="n"/>
+      <c r="C14" s="169" t="inlineStr">
+        <is>
+          <t>자료조사비</t>
+        </is>
+      </c>
+      <c r="D14" s="170" t="n"/>
+      <c r="E14" s="171" t="n"/>
+      <c r="F14" s="174" t="n"/>
+      <c r="G14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="43">
+      <c r="H14" s="172" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I14" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B15" s="168" t="n"/>
+      <c r="C15" s="175" t="inlineStr">
+        <is>
+          <t>프로젝트 매니저료</t>
+        </is>
+      </c>
+      <c r="D15" s="176" t="n"/>
+      <c r="E15" s="177" t="n"/>
+      <c r="F15" s="119" t="inlineStr">
+        <is>
+          <t>김미애</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="172" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I15" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="157" t="n"/>
+    </row>
+    <row r="16" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B16" s="114" t="inlineStr">
+        <is>
+          <t>정가항목 (A)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="178" t="n"/>
+      <c r="E16" s="179" t="n"/>
+      <c r="F16" s="70" t="n"/>
+      <c r="G16" s="70" t="n"/>
+      <c r="H16" s="180">
+        <f>SUM(H10:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="181">
+        <f>SUM(I10:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="181">
+        <f>SUM(J10:J15)</f>
+        <v/>
+      </c>
+      <c r="K16" s="96" t="inlineStr">
+        <is>
+          <t>광고대행사 정가항목 미적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B17" s="182" t="inlineStr">
+        <is>
+          <t>제작</t>
+        </is>
+      </c>
+      <c r="C17" s="183" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D17" s="183" t="inlineStr">
+        <is>
+          <t>Producer</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>크림치즈필름</t>
+        </is>
+      </c>
+      <c r="F17" s="184" t="n"/>
+      <c r="G17" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="165" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I17" s="165" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="J17" s="165" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="K17" s="82" t="n"/>
+      <c r="M17" s="185" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B18" s="168" t="n"/>
+      <c r="C18" s="183" t="inlineStr">
+        <is>
+          <t>프로덕션</t>
+        </is>
+      </c>
+      <c r="D18" s="183" t="inlineStr">
+        <is>
+          <t>CF 프로덕션</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>오드아이</t>
+        </is>
+      </c>
+      <c r="F18" s="184" t="n"/>
+      <c r="G18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="165" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I18" s="165" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="J18" s="165" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="K18" s="82" t="n"/>
+      <c r="M18" s="185" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B19" s="168" t="n"/>
+      <c r="C19" s="183" t="inlineStr">
+        <is>
+          <t>콘티</t>
+        </is>
+      </c>
+      <c r="D19" s="183" t="inlineStr">
+        <is>
+          <t>콘티/일러스트</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>투디</t>
+        </is>
+      </c>
+      <c r="F19" s="184" t="n"/>
+      <c r="G19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="165" t="n">
+        <v>65300000</v>
+      </c>
+      <c r="I19" s="165" t="n">
+        <v>65300000</v>
+      </c>
+      <c r="J19" s="165" t="n">
+        <v>65300000</v>
+      </c>
+      <c r="K19" s="82" t="n"/>
+      <c r="M19" s="185" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B20" s="168" t="n"/>
+      <c r="C20" s="186" t="inlineStr">
+        <is>
+          <t>Post프로덕션</t>
+        </is>
+      </c>
+      <c r="D20" s="183" t="inlineStr">
+        <is>
+          <t>NTC</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="184" t="n"/>
+      <c r="G20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="82" t="n"/>
+      <c r="M20" s="185" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B21" s="168" t="n"/>
+      <c r="C21" s="171" t="n"/>
+      <c r="D21" s="183" t="inlineStr">
+        <is>
+          <t>편집</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>포나인</t>
+        </is>
+      </c>
+      <c r="F21" s="184" t="n"/>
+      <c r="G21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="165" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I21" s="165" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="J21" s="165" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K21" s="82" t="n"/>
+      <c r="M21" s="185" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customFormat="1" customHeight="1" s="17">
+      <c r="B22" s="168" t="n"/>
+      <c r="C22" s="171" t="n"/>
+      <c r="D22" s="183" t="inlineStr">
+        <is>
+          <t>합성</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>포나인</t>
+        </is>
+      </c>
+      <c r="F22" s="184" t="n"/>
+      <c r="G22" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="165" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="I22" s="165" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="J22" s="165" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="K22" s="82" t="n"/>
+      <c r="M22" s="185" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B23" s="168" t="n"/>
+      <c r="C23" s="171" t="n"/>
+      <c r="D23" s="183" t="inlineStr">
+        <is>
+          <t>녹음실</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>킹콩</t>
+        </is>
+      </c>
+      <c r="F23" s="184" t="n"/>
+      <c r="G23" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="165" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="I23" s="165" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="J23" s="165" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="K23" s="82" t="n"/>
+      <c r="M23" s="185" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B24" s="168" t="n"/>
+      <c r="C24" s="171" t="n"/>
+      <c r="D24" s="183" t="inlineStr">
+        <is>
+          <t>오디오PD</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>레솔트뮤지끄</t>
+        </is>
+      </c>
+      <c r="F24" s="184" t="n"/>
+      <c r="G24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="165" t="n">
         <v>2000000</v>
       </c>
-      <c r="I12" s="89">
-        <v>0</v>
-      </c>
-      <c r="J12" s="89">
-        <v>0</v>
-      </c>
-      <c r="K12" s="108"/>
-    </row>
-    <row r="13" spans="2:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="105"/>
-      <c r="C13" s="122" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="123"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="21">
+      <c r="I24" s="165" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J24" s="165" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K24" s="82" t="n"/>
+      <c r="M24" s="185" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B25" s="187" t="n"/>
+      <c r="C25" s="171" t="n"/>
+      <c r="D25" s="183" t="inlineStr">
+        <is>
+          <t>성우</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>프리랜서</t>
+        </is>
+      </c>
+      <c r="F25" s="184" t="n"/>
+      <c r="G25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H25" s="165" t="n">
         <v>2000000</v>
       </c>
-      <c r="I13" s="88">
-        <v>0</v>
-      </c>
-      <c r="J13" s="88">
-        <v>0</v>
-      </c>
-      <c r="K13" s="109"/>
-    </row>
-    <row r="14" spans="2:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="105"/>
-      <c r="C14" s="122" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="123"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="19">
+      <c r="I25" s="165" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J25" s="165" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K25" s="82" t="n"/>
+      <c r="M25" s="185" t="n"/>
+    </row>
+    <row r="26" ht="15" customFormat="1" customHeight="1" s="17">
+      <c r="B26" s="104" t="inlineStr">
+        <is>
+          <t>저작권
+라이선스</t>
+        </is>
+      </c>
+      <c r="C26" s="183" t="inlineStr">
+        <is>
+          <t>BGM</t>
+        </is>
+      </c>
+      <c r="D26" s="183" t="inlineStr">
+        <is>
+          <t>라이브러리</t>
+        </is>
+      </c>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="188" t="n"/>
+      <c r="G26" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="43">
-        <v>250000</v>
-      </c>
-      <c r="I14" s="89">
-        <v>0</v>
-      </c>
-      <c r="J14" s="89">
-        <v>0</v>
-      </c>
-      <c r="K14" s="109"/>
-    </row>
-    <row r="15" spans="2:11" s="17" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="105"/>
-      <c r="C15" s="124" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="125"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="91" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="19">
-        <v>1</v>
-      </c>
-      <c r="H15" s="43">
-        <v>250000</v>
-      </c>
-      <c r="I15" s="89">
-        <v>0</v>
-      </c>
-      <c r="J15" s="89">
-        <v>0</v>
-      </c>
-      <c r="K15" s="110"/>
-    </row>
-    <row r="16" spans="2:11" s="17" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="93" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="44">
-        <f>SUM(H10:H15)</f>
-        <v>9500000</v>
-      </c>
-      <c r="I16" s="90">
-        <f>SUM(I10:I15)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="90">
-        <f>SUM(J10:J15)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="96" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="111" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="18">
-        <v>1</v>
-      </c>
-      <c r="H17" s="42">
-        <v>4000000</v>
-      </c>
-      <c r="I17" s="42">
-        <v>4000000</v>
-      </c>
-      <c r="J17" s="42">
-        <v>4000000</v>
-      </c>
-      <c r="K17" s="82"/>
-      <c r="M17" s="28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="105"/>
-      <c r="C18" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="32"/>
-      <c r="G18" s="18">
-        <v>1</v>
-      </c>
-      <c r="H18" s="42">
-        <v>40000000</v>
-      </c>
-      <c r="I18" s="42">
-        <v>36000000</v>
-      </c>
-      <c r="J18" s="42">
-        <v>36000000</v>
-      </c>
-      <c r="K18" s="82"/>
-      <c r="M18" s="28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="105"/>
-      <c r="C19" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="18">
-        <v>1</v>
-      </c>
-      <c r="H19" s="42">
-        <v>65300000</v>
-      </c>
-      <c r="I19" s="42">
-        <v>65300000</v>
-      </c>
-      <c r="J19" s="42">
-        <v>65300000</v>
-      </c>
-      <c r="K19" s="82"/>
-      <c r="M19" s="28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="105"/>
-      <c r="C20" s="102" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="23"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="18">
-        <v>1</v>
-      </c>
-      <c r="H20" s="42">
-        <v>0</v>
-      </c>
-      <c r="I20" s="42">
-        <v>0</v>
-      </c>
-      <c r="J20" s="42">
-        <v>0</v>
-      </c>
-      <c r="K20" s="82"/>
-      <c r="M20" s="28"/>
-    </row>
-    <row r="21" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="105"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="18">
-        <v>1</v>
-      </c>
-      <c r="H21" s="42">
-        <v>10000000</v>
-      </c>
-      <c r="I21" s="42">
-        <v>10000000</v>
-      </c>
-      <c r="J21" s="42">
-        <v>10000000</v>
-      </c>
-      <c r="K21" s="82"/>
-      <c r="M21" s="28"/>
-    </row>
-    <row r="22" spans="2:17" s="17" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="105"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="18">
-        <v>1</v>
-      </c>
-      <c r="H22" s="42">
-        <v>66000000</v>
-      </c>
-      <c r="I22" s="42">
-        <v>65000000</v>
-      </c>
-      <c r="J22" s="42">
-        <v>65000000</v>
-      </c>
-      <c r="K22" s="82"/>
-      <c r="M22" s="28"/>
-    </row>
-    <row r="23" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="105"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="18">
-        <v>1</v>
-      </c>
-      <c r="H23" s="42">
-        <v>6400000</v>
-      </c>
-      <c r="I23" s="42">
-        <v>6400000</v>
-      </c>
-      <c r="J23" s="42">
-        <v>6400000</v>
-      </c>
-      <c r="K23" s="82"/>
-      <c r="M23" s="28"/>
-    </row>
-    <row r="24" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="105"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="32"/>
-      <c r="G24" s="18">
-        <v>1</v>
-      </c>
-      <c r="H24" s="42">
-        <v>2000000</v>
-      </c>
-      <c r="I24" s="42">
-        <v>2000000</v>
-      </c>
-      <c r="J24" s="42">
-        <v>2000000</v>
-      </c>
-      <c r="K24" s="82"/>
-      <c r="M24" s="28"/>
-    </row>
-    <row r="25" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="112"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="18">
-        <v>1</v>
-      </c>
-      <c r="H25" s="42">
-        <v>2000000</v>
-      </c>
-      <c r="I25" s="42">
-        <v>2000000</v>
-      </c>
-      <c r="J25" s="42">
-        <v>2000000</v>
-      </c>
-      <c r="K25" s="82"/>
-      <c r="M25" s="28"/>
-    </row>
-    <row r="26" spans="2:17" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="104" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="54" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="18">
-        <v>1</v>
-      </c>
-      <c r="H26" s="45">
+      <c r="H26" s="189" t="n">
         <v>55000000</v>
       </c>
-      <c r="I26" s="45">
+      <c r="I26" s="189" t="n">
         <v>55000000</v>
       </c>
-      <c r="J26" s="45">
+      <c r="J26" s="189" t="n">
         <v>55000000</v>
       </c>
-      <c r="K26" s="98" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q26"/>
-    </row>
-    <row r="27" spans="2:17" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="B27" s="105"/>
-      <c r="C27" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="54"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="82"/>
-    </row>
-    <row r="28" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="105"/>
-      <c r="C28" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="54"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="72"/>
-    </row>
-    <row r="29" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="105"/>
-      <c r="C29" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="60"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="72"/>
-    </row>
-    <row r="30" spans="2:17" s="17" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="93" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="44">
+      <c r="K26" s="98" t="inlineStr">
+        <is>
+          <t>데이브레이크_넌언제나</t>
+        </is>
+      </c>
+      <c r="Q26" s="0" t="n"/>
+    </row>
+    <row r="27" ht="13.5" customFormat="1" customHeight="1" s="17">
+      <c r="B27" s="168" t="n"/>
+      <c r="C27" s="183" t="inlineStr">
+        <is>
+          <t>폰트</t>
+        </is>
+      </c>
+      <c r="D27" s="183" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="188" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="189" t="n"/>
+      <c r="I27" s="190" t="n"/>
+      <c r="J27" s="190" t="n"/>
+      <c r="K27" s="82" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B28" s="168" t="n"/>
+      <c r="C28" s="183" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="D28" s="183" t="n"/>
+      <c r="E28" s="38" t="n"/>
+      <c r="F28" s="188" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="189" t="n"/>
+      <c r="I28" s="190" t="n"/>
+      <c r="J28" s="190" t="n"/>
+      <c r="K28" s="72" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B29" s="168" t="n"/>
+      <c r="C29" s="191" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D29" s="191" t="n"/>
+      <c r="E29" s="38" t="n"/>
+      <c r="F29" s="188" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="189" t="n"/>
+      <c r="I29" s="190" t="n"/>
+      <c r="J29" s="190" t="n"/>
+      <c r="K29" s="72" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B30" s="114" t="inlineStr">
+        <is>
+          <t>외주항목계 (B)</t>
+        </is>
+      </c>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="53" t="n"/>
+      <c r="E30" s="179" t="n"/>
+      <c r="F30" s="70" t="n"/>
+      <c r="G30" s="70" t="n"/>
+      <c r="H30" s="180">
         <f>SUM(H17:H29)</f>
-        <v>250700000</v>
-      </c>
-      <c r="I30" s="44">
+        <v/>
+      </c>
+      <c r="I30" s="180">
         <f>SUM(I17:I29)</f>
-        <v>245700000</v>
-      </c>
-      <c r="J30" s="44">
+        <v/>
+      </c>
+      <c r="J30" s="180">
         <f>SUM(J17:J29)</f>
-        <v>245700000</v>
-      </c>
-      <c r="K30" s="71"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="28"/>
-    </row>
-    <row r="31" spans="2:17" s="17" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="83" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="84" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="84"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="87">
+        <v/>
+      </c>
+      <c r="K30" s="71" t="n"/>
+      <c r="L30" s="192" t="n"/>
+      <c r="M30" s="185" t="n"/>
+    </row>
+    <row r="31" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B31" s="83" t="inlineStr">
+        <is>
+          <t>대행수수료 (C)</t>
+        </is>
+      </c>
+      <c r="C31" s="84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (B)항목 * 17.65%</t>
+        </is>
+      </c>
+      <c r="D31" s="84" t="n"/>
+      <c r="E31" s="193" t="n"/>
+      <c r="F31" s="86" t="n"/>
+      <c r="G31" s="86" t="n"/>
+      <c r="H31" s="194">
         <f>H30*17.65%</f>
-        <v>44248550</v>
-      </c>
-      <c r="I31" s="87">
+        <v/>
+      </c>
+      <c r="I31" s="194">
         <f>I30*10%</f>
-        <v>24570000</v>
-      </c>
-      <c r="J31" s="87">
+        <v/>
+      </c>
+      <c r="J31" s="194">
         <f>J30*10%</f>
-        <v>24570000</v>
-      </c>
-      <c r="K31" s="97" t="s">
-        <v>93</v>
-      </c>
-      <c r="L31" s="28"/>
-    </row>
-    <row r="32" spans="2:17" s="15" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="46">
+        <v/>
+      </c>
+      <c r="K31" s="97" t="inlineStr">
+        <is>
+          <t>광고대행사 대행수수료 조정 (17.65% → 10%)</t>
+        </is>
+      </c>
+      <c r="L31" s="185" t="n"/>
+    </row>
+    <row r="32" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>합계금액</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (A)+(B)+(C)</t>
+        </is>
+      </c>
+      <c r="D32" s="34" t="n"/>
+      <c r="E32" s="195" t="n"/>
+      <c r="F32" s="36" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="196">
         <f>H16+H30+H31</f>
-        <v>304448550</v>
-      </c>
-      <c r="I32" s="46">
+        <v/>
+      </c>
+      <c r="I32" s="196">
         <f>I16+I30+I31</f>
-        <v>270270000</v>
-      </c>
-      <c r="J32" s="46">
+        <v/>
+      </c>
+      <c r="J32" s="196">
         <f>J16+J30+J31</f>
-        <v>270270000</v>
-      </c>
-      <c r="K32" s="73"/>
-    </row>
-    <row r="33" spans="2:13" s="61" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="64" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="65"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="67"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="68">
+        <v/>
+      </c>
+      <c r="K32" s="73" t="n"/>
+    </row>
+    <row r="33" ht="23.25" customFormat="1" customHeight="1" s="61" thickBot="1">
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>청구금액</t>
+        </is>
+      </c>
+      <c r="C33" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (VAT 포함)</t>
+        </is>
+      </c>
+      <c r="D33" s="65" t="n"/>
+      <c r="E33" s="197" t="n"/>
+      <c r="F33" s="67" t="n"/>
+      <c r="G33" s="67" t="n"/>
+      <c r="H33" s="198">
         <f>H32*1.1</f>
-        <v>334893405</v>
-      </c>
-      <c r="I33" s="68">
+        <v/>
+      </c>
+      <c r="I33" s="198">
         <f>I32*1.1</f>
-        <v>297297000</v>
-      </c>
-      <c r="J33" s="68">
+        <v/>
+      </c>
+      <c r="J33" s="198">
         <f>J32*1.1</f>
-        <v>297297000</v>
-      </c>
-      <c r="K33" s="69"/>
-      <c r="M33" s="62" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="106"/>
-      <c r="C34" s="106"/>
-      <c r="D34" s="106"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="106"/>
-      <c r="I34" s="106"/>
-      <c r="J34" s="106"/>
-      <c r="K34" s="106"/>
-      <c r="M34" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H35" s="27"/>
-      <c r="I35" s="80"/>
-      <c r="J35" s="80"/>
-      <c r="K35" s="26"/>
-      <c r="M35" s="31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H36" s="24"/>
-    </row>
-    <row r="38" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-    </row>
-    <row r="39" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
-    </row>
-    <row r="41" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="30"/>
-      <c r="G41" s="29"/>
-    </row>
-    <row r="46" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E46" s="24"/>
+        <v/>
+      </c>
+      <c r="K33" s="69" t="n"/>
+      <c r="M33" s="199" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1" s="156">
+      <c r="B34" s="106" t="n"/>
+      <c r="C34" s="200" t="n"/>
+      <c r="D34" s="200" t="n"/>
+      <c r="E34" s="200" t="n"/>
+      <c r="F34" s="200" t="n"/>
+      <c r="G34" s="200" t="n"/>
+      <c r="H34" s="200" t="n"/>
+      <c r="I34" s="200" t="n"/>
+      <c r="J34" s="200" t="n"/>
+      <c r="K34" s="200" t="n"/>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1" s="156">
+      <c r="H35" s="201" t="n"/>
+      <c r="I35" s="202" t="n"/>
+      <c r="J35" s="202" t="n"/>
+      <c r="K35" s="203" t="n"/>
+      <c r="M35" s="204" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1" s="156">
+      <c r="H36" s="205" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="14.25" customHeight="1" s="156">
+      <c r="H38" s="205" t="n"/>
+      <c r="I38" s="205" t="n"/>
+      <c r="J38" s="205" t="n"/>
+    </row>
+    <row r="39" ht="14.25" customHeight="1" s="156">
+      <c r="I39" s="206" t="n"/>
+      <c r="J39" s="206" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="14.25" customHeight="1" s="156">
+      <c r="D41" s="30" t="n"/>
+      <c r="G41" s="207" t="n"/>
+    </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46" ht="14.25" customHeight="1" s="156">
+      <c r="E46" s="205" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="F10:F14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B1:K1"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C20:C25"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B17:B25"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E10:E15"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="F10:F14"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="B26:B29"/>
     <mergeCell ref="B34:K34"/>
     <mergeCell ref="K10:K15"/>
-    <mergeCell ref="B17:B25"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.35433070866141736" bottom="0.2" header="0.19685039370078741" footer="0.23"/>
-  <pageSetup paperSize="8" orientation="landscape" verticalDpi="200" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.1574803149606299" right="0.1574803149606299" top="0.3543307086614174" bottom="0.2" header="0.1968503937007874" footer="0.23"/>
+  <pageSetup orientation="landscape" paperSize="8" verticalDpi="200"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M52"/>
-  <sheetFormatPr defaultColWidth="7.88671875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M52"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="7.88671875" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="5" customWidth="1"/>
-    <col min="9" max="10" width="12.88671875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="32.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="0.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="7.88671875" style="1"/>
+    <col width="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="11.109375" customWidth="1" style="2" min="2" max="2"/>
+    <col width="11.109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="20.44140625" customWidth="1" style="4" min="4" max="4"/>
+    <col width="12.33203125" customWidth="1" style="5" min="5" max="5"/>
+    <col width="11.109375" customWidth="1" style="2" min="6" max="6"/>
+    <col width="8.44140625" customWidth="1" style="2" min="7" max="7"/>
+    <col width="12.44140625" customWidth="1" style="5" min="8" max="8"/>
+    <col width="12.88671875" customWidth="1" style="5" min="9" max="10"/>
+    <col width="32.88671875" bestFit="1" customWidth="1" style="5" min="11" max="11"/>
+    <col width="0.88671875" customWidth="1" style="1" min="12" max="12"/>
+    <col width="15.33203125" customWidth="1" style="1" min="13" max="13"/>
+    <col width="7.88671875" customWidth="1" style="1" min="14" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="127" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-    </row>
-    <row r="2" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="128" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="131" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="132"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="134" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
-    </row>
-    <row r="3" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="74" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="136"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="138" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="139"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="137" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="147"/>
-      <c r="K3" s="148"/>
-    </row>
-    <row r="4" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="136"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="137" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="147"/>
-      <c r="K4" s="148"/>
-    </row>
-    <row r="5" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="141"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="137" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="147"/>
-      <c r="K5" s="148"/>
-    </row>
-    <row r="6" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="76" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="149">
+    <row r="1" ht="48" customHeight="1" s="156" thickBot="1">
+      <c r="B1" s="127" t="inlineStr">
+        <is>
+          <t>제작비 명세서</t>
+        </is>
+      </c>
+      <c r="C1" s="157" t="n"/>
+      <c r="D1" s="157" t="n"/>
+      <c r="E1" s="157" t="n"/>
+      <c r="F1" s="157" t="n"/>
+      <c r="G1" s="157" t="n"/>
+      <c r="H1" s="157" t="n"/>
+      <c r="I1" s="157" t="n"/>
+      <c r="J1" s="157" t="n"/>
+      <c r="K1" s="157" t="n"/>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" s="156">
+      <c r="B2" s="128" t="inlineStr">
+        <is>
+          <t>공급받는자</t>
+        </is>
+      </c>
+      <c r="C2" s="208" t="n"/>
+      <c r="D2" s="209" t="n"/>
+      <c r="E2" s="210" t="inlineStr">
+        <is>
+          <t>[CM영상제작 표준 견적서 ]</t>
+        </is>
+      </c>
+      <c r="F2" s="208" t="n"/>
+      <c r="G2" s="211" t="n"/>
+      <c r="H2" s="135" t="inlineStr">
+        <is>
+          <t>공급자</t>
+        </is>
+      </c>
+      <c r="I2" s="208" t="n"/>
+      <c r="J2" s="208" t="n"/>
+      <c r="K2" s="211" t="n"/>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" s="156">
+      <c r="B3" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENT </t>
+        </is>
+      </c>
+      <c r="C3" s="136" t="n"/>
+      <c r="D3" s="212" t="n"/>
+      <c r="E3" s="213" t="inlineStr">
+        <is>
+          <t>아래와 같이
+견적 합니다.</t>
+        </is>
+      </c>
+      <c r="F3" s="214" t="n"/>
+      <c r="G3" s="215" t="n"/>
+      <c r="H3" s="75" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="I3" s="216" t="inlineStr">
+        <is>
+          <t>(주)광고대행사</t>
+        </is>
+      </c>
+      <c r="J3" s="217" t="n"/>
+      <c r="K3" s="218" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" s="156">
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>Job Name</t>
+        </is>
+      </c>
+      <c r="C4" s="136" t="n"/>
+      <c r="D4" s="212" t="n"/>
+      <c r="E4" s="219" t="n"/>
+      <c r="G4" s="220" t="n"/>
+      <c r="H4" s="75" t="inlineStr">
+        <is>
+          <t>대표이사</t>
+        </is>
+      </c>
+      <c r="I4" s="216" t="inlineStr">
+        <is>
+          <t>유 정 근</t>
+        </is>
+      </c>
+      <c r="J4" s="217" t="n"/>
+      <c r="K4" s="218" t="n"/>
+    </row>
+    <row r="5" ht="22.5" customHeight="1" s="156">
+      <c r="B5" s="74" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="C5" s="136" t="n"/>
+      <c r="D5" s="212" t="n"/>
+      <c r="E5" s="219" t="n"/>
+      <c r="G5" s="220" t="n"/>
+      <c r="H5" s="75" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="I5" s="216" t="inlineStr">
+        <is>
+          <t>202-81-45960</t>
+        </is>
+      </c>
+      <c r="J5" s="217" t="n"/>
+      <c r="K5" s="218" t="n"/>
+    </row>
+    <row r="6" ht="22.5" customHeight="1" s="156">
+      <c r="B6" s="76" t="inlineStr">
+        <is>
+          <t>견적금액</t>
+        </is>
+      </c>
+      <c r="C6" s="221">
         <f>I39</f>
-        <v>275638000</v>
-      </c>
-      <c r="D6" s="150"/>
-      <c r="E6" s="141"/>
-      <c r="F6" s="142"/>
-      <c r="G6" s="143"/>
-      <c r="H6" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="137" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="147"/>
-      <c r="K6" s="148"/>
-    </row>
-    <row r="7" spans="2:11" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="151"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="144"/>
-      <c r="F7" s="145"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="153" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="154"/>
-      <c r="K7" s="155"/>
-    </row>
-    <row r="8" spans="2:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-    </row>
-    <row r="10" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="49"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-    </row>
-    <row r="11" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" s="51"/>
-    </row>
-    <row r="12" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="J12" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="K12" s="49"/>
-    </row>
-    <row r="13" spans="2:11" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="57"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="59"/>
-    </row>
-    <row r="14" spans="2:11" s="8" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="126"/>
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126"/>
-      <c r="K14" s="126"/>
-    </row>
-    <row r="15" spans="2:11" s="17" customFormat="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="100" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="113" t="s">
+        <v/>
+      </c>
+      <c r="D6" s="218" t="n"/>
+      <c r="E6" s="219" t="n"/>
+      <c r="G6" s="220" t="n"/>
+      <c r="H6" s="75" t="inlineStr">
+        <is>
+          <t>사업장주소</t>
+        </is>
+      </c>
+      <c r="I6" s="216" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로 222 (한남동)</t>
+        </is>
+      </c>
+      <c r="J6" s="217" t="n"/>
+      <c r="K6" s="218" t="n"/>
+    </row>
+    <row r="7" ht="52.5" customHeight="1" s="156" thickBot="1">
+      <c r="B7" s="77" t="inlineStr">
+        <is>
+          <t>담당자/연락처</t>
+        </is>
+      </c>
+      <c r="C7" s="151" t="n"/>
+      <c r="D7" s="222" t="n"/>
+      <c r="E7" s="223" t="n"/>
+      <c r="F7" s="157" t="n"/>
+      <c r="G7" s="224" t="n"/>
+      <c r="H7" s="78" t="inlineStr">
+        <is>
+          <t>담당자/연락처</t>
+        </is>
+      </c>
+      <c r="I7" s="225" t="inlineStr">
+        <is>
+          <t>우경훈 프로
+권두인 프로
+조영찬 프로</t>
+        </is>
+      </c>
+      <c r="J7" s="159" t="n"/>
+      <c r="K7" s="226" t="n"/>
+    </row>
+    <row r="8" ht="12" customHeight="1" s="156">
+      <c r="C8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Job :</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="47" t="n"/>
+      <c r="F9" s="48" t="n"/>
+      <c r="G9" s="48" t="n"/>
+      <c r="H9" s="47" t="n"/>
+      <c r="I9" s="47" t="n"/>
+      <c r="J9" s="47" t="n"/>
+      <c r="K9" s="47" t="n"/>
+    </row>
+    <row r="10" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Job Name :</t>
+        </is>
+      </c>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>매체 :</t>
+        </is>
+      </c>
+      <c r="G10" s="49" t="inlineStr">
+        <is>
+          <t>30", 15" 등</t>
+        </is>
+      </c>
+      <c r="H10" s="49" t="n"/>
+      <c r="I10" s="50" t="n"/>
+      <c r="J10" s="50" t="n"/>
+      <c r="K10" s="50" t="n"/>
+    </row>
+    <row r="11" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>CD(제작팀) :</t>
+        </is>
+      </c>
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>박현정</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD : </t>
+        </is>
+      </c>
+      <c r="E11" s="51" t="inlineStr">
+        <is>
+          <t>오창규 등</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CW : </t>
+        </is>
+      </c>
+      <c r="G11" s="51" t="inlineStr">
+        <is>
+          <t>박지환 등</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE : </t>
+        </is>
+      </c>
+      <c r="I11" s="51" t="inlineStr">
+        <is>
+          <t>이재환, 우경훈, 권두인 조영찬</t>
+        </is>
+      </c>
+      <c r="J11" s="51" t="inlineStr">
+        <is>
+          <t>이재환, 우경훈, 권두인 조영찬</t>
+        </is>
+      </c>
+      <c r="K11" s="51" t="n"/>
+    </row>
+    <row r="12" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>협력업체 :</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="50" t="n"/>
+      <c r="G12" s="50" t="n"/>
+      <c r="H12" s="95" t="inlineStr">
+        <is>
+          <t>PM :</t>
+        </is>
+      </c>
+      <c r="I12" s="49" t="inlineStr">
+        <is>
+          <t>김미애</t>
+        </is>
+      </c>
+      <c r="J12" s="49" t="inlineStr">
+        <is>
+          <t>김미애</t>
+        </is>
+      </c>
+      <c r="K12" s="49" t="n"/>
+    </row>
+    <row r="13" ht="18" customFormat="1" customHeight="1" s="8">
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>촬영일 :</t>
+        </is>
+      </c>
+      <c r="C13" s="158" t="n"/>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>On-Air :</t>
+        </is>
+      </c>
+      <c r="E13" s="57" t="n"/>
+      <c r="F13" s="58" t="n"/>
+      <c r="G13" s="58" t="n"/>
+      <c r="H13" s="59" t="n"/>
+      <c r="I13" s="59" t="n"/>
+      <c r="J13" s="59" t="n"/>
+      <c r="K13" s="59" t="n"/>
+    </row>
+    <row r="14" ht="13.5" customFormat="1" customHeight="1" s="8" thickBot="1">
+      <c r="B14" s="126" t="n"/>
+      <c r="C14" s="159" t="n"/>
+      <c r="D14" s="159" t="n"/>
+      <c r="E14" s="159" t="n"/>
+      <c r="F14" s="159" t="n"/>
+      <c r="G14" s="159" t="n"/>
+      <c r="H14" s="159" t="n"/>
+      <c r="I14" s="159" t="n"/>
+      <c r="J14" s="159" t="n"/>
+      <c r="K14" s="159" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="17" thickBot="1">
+      <c r="B15" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제 작 항 목 </t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>세부내용</t>
+        </is>
+      </c>
+      <c r="D15" s="160" t="n"/>
+      <c r="E15" s="113" t="inlineStr">
+        <is>
+          <t>협력회사</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="G15" s="114" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="H15" s="41" t="inlineStr">
+        <is>
+          <t>1차 사전견적</t>
+        </is>
+      </c>
+      <c r="I15" s="41" t="inlineStr">
+        <is>
+          <t>2차 사전견적</t>
+        </is>
+      </c>
+      <c r="J15" s="41" t="inlineStr">
+        <is>
+          <t>조정견적</t>
+        </is>
+      </c>
+      <c r="K15" s="70" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B16" s="104" t="inlineStr">
+        <is>
+          <t>정가항목</t>
+        </is>
+      </c>
+      <c r="C16" s="161" t="inlineStr">
+        <is>
+          <t>기 획 료</t>
+        </is>
+      </c>
+      <c r="D16" s="162" t="n"/>
+      <c r="E16" s="163" t="inlineStr">
+        <is>
+          <t>광고대행사
+(작품당)</t>
+        </is>
+      </c>
+      <c r="F16" s="164" t="inlineStr">
+        <is>
+          <t>이재환
+김형운
+조영찬
+권두인</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="165" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I16" s="166" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="114"/>
-      <c r="E15" s="99" t="s">
+      <c r="J16" s="166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="167" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B17" s="168" t="n"/>
+      <c r="C17" s="169" t="inlineStr">
+        <is>
+          <t>COPY료</t>
+        </is>
+      </c>
+      <c r="D17" s="170" t="n"/>
+      <c r="E17" s="171" t="n"/>
+      <c r="F17" s="171" t="n"/>
+      <c r="G17" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="100" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" s="41" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" s="70" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="104" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="115" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="116"/>
-      <c r="E16" s="117" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="117" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="18">
+      <c r="H17" s="172" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I17" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B18" s="168" t="n"/>
+      <c r="C18" s="169" t="inlineStr">
+        <is>
+          <t>Creative Work료</t>
+        </is>
+      </c>
+      <c r="D18" s="170" t="n"/>
+      <c r="E18" s="171" t="n"/>
+      <c r="F18" s="171" t="n"/>
+      <c r="G18" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="42">
-        <v>3000000</v>
-      </c>
-      <c r="I16" s="88">
+      <c r="H18" s="172" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I18" s="173" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="88">
+      <c r="J18" s="173" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="107"/>
-    </row>
-    <row r="17" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="105"/>
-      <c r="C17" s="122" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="123"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="20">
+    </row>
+    <row r="19" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B19" s="168" t="n"/>
+      <c r="C19" s="169" t="inlineStr">
+        <is>
+          <t>Direction료</t>
+        </is>
+      </c>
+      <c r="D19" s="170" t="n"/>
+      <c r="E19" s="171" t="n"/>
+      <c r="F19" s="171" t="n"/>
+      <c r="G19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="43">
+      <c r="H19" s="165" t="n">
         <v>2000000</v>
       </c>
-      <c r="I17" s="89">
+      <c r="I19" s="166" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="89">
+      <c r="J19" s="166" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="108"/>
-    </row>
-    <row r="18" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="105"/>
-      <c r="C18" s="122" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="123"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="21">
+    </row>
+    <row r="20" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B20" s="168" t="n"/>
+      <c r="C20" s="169" t="inlineStr">
+        <is>
+          <t>자료조사비</t>
+        </is>
+      </c>
+      <c r="D20" s="170" t="n"/>
+      <c r="E20" s="171" t="n"/>
+      <c r="F20" s="174" t="n"/>
+      <c r="G20" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="43">
-        <v>2000000</v>
-      </c>
-      <c r="I18" s="89">
+      <c r="H20" s="172" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I20" s="173" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="89">
+      <c r="J20" s="173" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="108"/>
-    </row>
-    <row r="19" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="105"/>
-      <c r="C19" s="122" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="123"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="21">
+    </row>
+    <row r="21" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B21" s="168" t="n"/>
+      <c r="C21" s="175" t="inlineStr">
+        <is>
+          <t>프로젝트 매니저료</t>
+        </is>
+      </c>
+      <c r="D21" s="176" t="n"/>
+      <c r="E21" s="177" t="n"/>
+      <c r="F21" s="119" t="inlineStr">
+        <is>
+          <t>김미애</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="42">
-        <v>2000000</v>
-      </c>
-      <c r="I19" s="88">
+      <c r="H21" s="172" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I21" s="173" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="88">
+      <c r="J21" s="173" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="109"/>
-    </row>
-    <row r="20" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="105"/>
-      <c r="C20" s="122" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="123"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="19">
+      <c r="K21" s="157" t="n"/>
+    </row>
+    <row r="22" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B22" s="114" t="inlineStr">
+        <is>
+          <t>정가항목 (A)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="178" t="n"/>
+      <c r="E22" s="179" t="n"/>
+      <c r="F22" s="70" t="n"/>
+      <c r="G22" s="70" t="n"/>
+      <c r="H22" s="180">
+        <f>SUM(H16:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="181">
+        <f>SUM(I16:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="181">
+        <f>SUM(J16:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="96" t="inlineStr">
+        <is>
+          <t>광고대행사 정가항목 미적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B23" s="182" t="inlineStr">
+        <is>
+          <t>제작</t>
+        </is>
+      </c>
+      <c r="C23" s="183" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D23" s="183" t="inlineStr">
+        <is>
+          <t>Producer</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>크림치즈필름</t>
+        </is>
+      </c>
+      <c r="F23" s="184" t="n"/>
+      <c r="G23" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="43">
-        <v>250000</v>
-      </c>
-      <c r="I20" s="89">
+      <c r="H23" s="165" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I23" s="227" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="J23" s="227" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="K23" s="82" t="n"/>
+      <c r="M23" s="185" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B24" s="168" t="n"/>
+      <c r="C24" s="183" t="inlineStr">
+        <is>
+          <t>프로덕션</t>
+        </is>
+      </c>
+      <c r="D24" s="183" t="inlineStr">
+        <is>
+          <t>CF 프로덕션</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>오드아이</t>
+        </is>
+      </c>
+      <c r="F24" s="184" t="n"/>
+      <c r="G24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="165" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I24" s="227" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="J24" s="227" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="K24" s="82" t="n"/>
+      <c r="M24" s="185" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B25" s="168" t="n"/>
+      <c r="C25" s="183" t="inlineStr">
+        <is>
+          <t>프로덕션</t>
+        </is>
+      </c>
+      <c r="D25" s="183" t="inlineStr">
+        <is>
+          <t>콘티/일러스트</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>이동건</t>
+        </is>
+      </c>
+      <c r="F25" s="184" t="n"/>
+      <c r="G25" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="165" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="I25" s="227" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="J25" s="227" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="K25" s="82" t="n"/>
+      <c r="M25" s="185" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B26" s="168" t="n"/>
+      <c r="C26" s="186" t="inlineStr">
+        <is>
+          <t>Post프로덕션</t>
+        </is>
+      </c>
+      <c r="D26" s="183" t="inlineStr">
+        <is>
+          <t>NTC</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="184" t="n"/>
+      <c r="G26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="165" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="89">
+      <c r="I26" s="227" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="109"/>
-    </row>
-    <row r="21" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="105"/>
-      <c r="C21" s="124" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="125"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="101" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="J26" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="82" t="n"/>
+      <c r="M26" s="185" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B27" s="168" t="n"/>
+      <c r="C27" s="171" t="n"/>
+      <c r="D27" s="183" t="inlineStr">
+        <is>
+          <t>편집</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>포나인</t>
+        </is>
+      </c>
+      <c r="F27" s="184" t="n"/>
+      <c r="G27" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="43">
-        <v>250000</v>
-      </c>
-      <c r="I21" s="89">
-        <v>0</v>
-      </c>
-      <c r="J21" s="89">
-        <v>0</v>
-      </c>
-      <c r="K21" s="110"/>
-    </row>
-    <row r="22" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="100" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="44">
-        <f>SUM(H16:H21)</f>
-        <v>9500000</v>
-      </c>
-      <c r="I22" s="90">
-        <f>SUM(I16:I21)</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="90">
-        <f>SUM(J16:J21)</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="96" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="111" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="18">
+      <c r="H27" s="165" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="I27" s="227" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="J27" s="227" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="K27" s="82" t="n"/>
+      <c r="M27" s="185" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customFormat="1" customHeight="1" s="17">
+      <c r="B28" s="168" t="n"/>
+      <c r="C28" s="171" t="n"/>
+      <c r="D28" s="183" t="inlineStr">
+        <is>
+          <t>합성</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>포나인</t>
+        </is>
+      </c>
+      <c r="F28" s="184" t="n"/>
+      <c r="G28" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="42">
-        <v>4000000</v>
-      </c>
-      <c r="I23" s="94">
-        <v>4000000</v>
-      </c>
-      <c r="J23" s="94">
-        <v>4000000</v>
-      </c>
-      <c r="K23" s="82"/>
-      <c r="M23" s="28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="105"/>
-      <c r="C24" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="32"/>
-      <c r="G24" s="18">
+      <c r="H28" s="165" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="I28" s="228" t="n">
+        <v>40400000</v>
+      </c>
+      <c r="J28" s="228" t="n">
+        <v>40400000</v>
+      </c>
+      <c r="K28" s="82" t="n"/>
+      <c r="M28" s="185" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B29" s="168" t="n"/>
+      <c r="C29" s="171" t="n"/>
+      <c r="D29" s="183" t="inlineStr">
+        <is>
+          <t>녹음실</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>킹콩</t>
+        </is>
+      </c>
+      <c r="F29" s="184" t="n"/>
+      <c r="G29" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="42">
-        <v>40000000</v>
-      </c>
-      <c r="I24" s="94">
-        <v>36000000</v>
-      </c>
-      <c r="J24" s="94">
-        <v>36000000</v>
-      </c>
-      <c r="K24" s="82"/>
-      <c r="M24" s="28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="105"/>
-      <c r="C25" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="18">
+      <c r="H29" s="165" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="I29" s="228" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="J29" s="228" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="K29" s="82" t="n"/>
+      <c r="M29" s="185" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B30" s="168" t="n"/>
+      <c r="C30" s="171" t="n"/>
+      <c r="D30" s="183" t="inlineStr">
+        <is>
+          <t>오디오PD</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>레솔트뮤지끄</t>
+        </is>
+      </c>
+      <c r="F30" s="184" t="n"/>
+      <c r="G30" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="42">
-        <v>78000000</v>
-      </c>
-      <c r="I25" s="94">
-        <v>78000000</v>
-      </c>
-      <c r="J25" s="94">
-        <v>78000000</v>
-      </c>
-      <c r="K25" s="82"/>
-      <c r="M25" s="28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="105"/>
-      <c r="C26" s="102" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="23"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="18">
+      <c r="H30" s="165" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I30" s="228" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="J30" s="228" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="K30" s="82" t="n"/>
+      <c r="M30" s="185" t="n"/>
+    </row>
+    <row r="31" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B31" s="187" t="n"/>
+      <c r="C31" s="171" t="n"/>
+      <c r="D31" s="183" t="inlineStr">
+        <is>
+          <t>성우</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>프리랜서</t>
+        </is>
+      </c>
+      <c r="F31" s="184" t="n"/>
+      <c r="G31" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="42">
-        <v>0</v>
-      </c>
-      <c r="I26" s="94">
-        <v>0</v>
-      </c>
-      <c r="J26" s="94">
-        <v>0</v>
-      </c>
-      <c r="K26" s="82"/>
-      <c r="M26" s="28"/>
-    </row>
-    <row r="27" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="105"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F27" s="32"/>
-      <c r="G27" s="18">
+      <c r="H31" s="165" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I31" s="228" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J31" s="228" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K31" s="82" t="n"/>
+      <c r="M31" s="185" t="n"/>
+    </row>
+    <row r="32" ht="15" customFormat="1" customHeight="1" s="17">
+      <c r="B32" s="104" t="inlineStr">
+        <is>
+          <t>저작권
+라이선스</t>
+        </is>
+      </c>
+      <c r="C32" s="183" t="inlineStr">
+        <is>
+          <t>BGM</t>
+        </is>
+      </c>
+      <c r="D32" s="183" t="inlineStr">
+        <is>
+          <t>라이브러리</t>
+        </is>
+      </c>
+      <c r="E32" s="38" t="n"/>
+      <c r="F32" s="188" t="n"/>
+      <c r="G32" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="42">
-        <v>7500000</v>
-      </c>
-      <c r="I27" s="94">
-        <v>7500000</v>
-      </c>
-      <c r="J27" s="94">
-        <v>7500000</v>
-      </c>
-      <c r="K27" s="82"/>
-      <c r="M27" s="28"/>
-    </row>
-    <row r="28" spans="2:13" s="17" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="105"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F28" s="32"/>
-      <c r="G28" s="18">
-        <v>1</v>
-      </c>
-      <c r="H28" s="42">
+      <c r="H32" s="189" t="n">
         <v>55000000</v>
       </c>
-      <c r="I28" s="39">
-        <v>40400000</v>
-      </c>
-      <c r="J28" s="39">
-        <v>40400000</v>
-      </c>
-      <c r="K28" s="82"/>
-      <c r="M28" s="28"/>
-    </row>
-    <row r="29" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="105"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="F29" s="32"/>
-      <c r="G29" s="18">
-        <v>1</v>
-      </c>
-      <c r="H29" s="42">
-        <v>4700000</v>
-      </c>
-      <c r="I29" s="39">
-        <v>4700000</v>
-      </c>
-      <c r="J29" s="39">
-        <v>4700000</v>
-      </c>
-      <c r="K29" s="82"/>
-      <c r="M29" s="28"/>
-    </row>
-    <row r="30" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="105"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="F30" s="32"/>
-      <c r="G30" s="18">
-        <v>1</v>
-      </c>
-      <c r="H30" s="42">
-        <v>1200000</v>
-      </c>
-      <c r="I30" s="39">
-        <v>1200000</v>
-      </c>
-      <c r="J30" s="39">
-        <v>1200000</v>
-      </c>
-      <c r="K30" s="82"/>
-      <c r="M30" s="28"/>
-    </row>
-    <row r="31" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="112"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="32"/>
-      <c r="G31" s="18">
-        <v>1</v>
-      </c>
-      <c r="H31" s="42">
-        <v>1000000</v>
-      </c>
-      <c r="I31" s="39">
-        <v>1000000</v>
-      </c>
-      <c r="J31" s="39">
-        <v>1000000</v>
-      </c>
-      <c r="K31" s="82"/>
-      <c r="M31" s="28"/>
-    </row>
-    <row r="32" spans="2:13" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="104" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="54" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="18">
-        <v>1</v>
-      </c>
-      <c r="H32" s="45">
+      <c r="I32" s="190" t="n">
         <v>55000000</v>
       </c>
-      <c r="I32" s="40">
+      <c r="J32" s="190" t="n">
         <v>55000000</v>
       </c>
-      <c r="J32" s="40">
-        <v>55000000</v>
-      </c>
-      <c r="K32" s="98" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="B33" s="105"/>
-      <c r="C33" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="54"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="82"/>
-    </row>
-    <row r="34" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="105"/>
-      <c r="C34" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="54"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="72"/>
-    </row>
-    <row r="35" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="105"/>
-      <c r="C35" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="60"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="72"/>
-    </row>
-    <row r="36" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="100" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="52"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="44">
+      <c r="K32" s="98" t="inlineStr">
+        <is>
+          <t>데이브레이크_들었다놨다</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="13.5" customFormat="1" customHeight="1" s="17">
+      <c r="B33" s="168" t="n"/>
+      <c r="C33" s="183" t="inlineStr">
+        <is>
+          <t>폰트</t>
+        </is>
+      </c>
+      <c r="D33" s="183" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="F33" s="188" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="189" t="n"/>
+      <c r="I33" s="190" t="n"/>
+      <c r="J33" s="190" t="n"/>
+      <c r="K33" s="82" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customFormat="1" customHeight="1" s="17">
+      <c r="B34" s="168" t="n"/>
+      <c r="C34" s="183" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="D34" s="183" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="188" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="189" t="n"/>
+      <c r="I34" s="190" t="n"/>
+      <c r="J34" s="190" t="n"/>
+      <c r="K34" s="72" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B35" s="168" t="n"/>
+      <c r="C35" s="191" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D35" s="191" t="n"/>
+      <c r="E35" s="38" t="n"/>
+      <c r="F35" s="188" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="189" t="n"/>
+      <c r="I35" s="190" t="n"/>
+      <c r="J35" s="190" t="n"/>
+      <c r="K35" s="72" t="n"/>
+    </row>
+    <row r="36" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B36" s="114" t="inlineStr">
+        <is>
+          <t>외주항목계 (B)</t>
+        </is>
+      </c>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="53" t="n"/>
+      <c r="E36" s="179" t="n"/>
+      <c r="F36" s="70" t="n"/>
+      <c r="G36" s="70" t="n"/>
+      <c r="H36" s="180">
         <f>SUM(H23:H35)</f>
-        <v>246400000</v>
-      </c>
-      <c r="I36" s="44">
+        <v/>
+      </c>
+      <c r="I36" s="180">
         <f>SUM(I23:I35)</f>
-        <v>227800000</v>
-      </c>
-      <c r="J36" s="44">
+        <v/>
+      </c>
+      <c r="J36" s="180">
         <f>SUM(J23:J35)</f>
-        <v>227800000</v>
-      </c>
-      <c r="K36" s="71"/>
-      <c r="L36" s="37"/>
-      <c r="M36" s="28"/>
-    </row>
-    <row r="37" spans="2:13" s="17" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="83" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="84"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="86"/>
-      <c r="G37" s="86"/>
-      <c r="H37" s="87">
+        <v/>
+      </c>
+      <c r="K36" s="71" t="n"/>
+      <c r="L36" s="192" t="n"/>
+      <c r="M36" s="185" t="n"/>
+    </row>
+    <row r="37" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B37" s="83" t="inlineStr">
+        <is>
+          <t>대행수수료 (C)</t>
+        </is>
+      </c>
+      <c r="C37" s="84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (B)항목 * 17.65%</t>
+        </is>
+      </c>
+      <c r="D37" s="84" t="n"/>
+      <c r="E37" s="193" t="n"/>
+      <c r="F37" s="86" t="n"/>
+      <c r="G37" s="86" t="n"/>
+      <c r="H37" s="194">
         <f>H36*17.65%</f>
-        <v>43489600</v>
-      </c>
-      <c r="I37" s="87">
+        <v/>
+      </c>
+      <c r="I37" s="194">
         <f>I36*10%</f>
-        <v>22780000</v>
-      </c>
-      <c r="J37" s="87">
+        <v/>
+      </c>
+      <c r="J37" s="194">
         <f>J36*10%</f>
-        <v>22780000</v>
-      </c>
-      <c r="K37" s="97" t="s">
-        <v>93</v>
-      </c>
-      <c r="L37" s="28"/>
-    </row>
-    <row r="38" spans="2:13" s="15" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" s="34"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="46">
+        <v/>
+      </c>
+      <c r="K37" s="97" t="inlineStr">
+        <is>
+          <t>광고대행사 대행수수료 조정 (17.65% → 10%)</t>
+        </is>
+      </c>
+      <c r="L37" s="185" t="n"/>
+    </row>
+    <row r="38" ht="16.5" customFormat="1" customHeight="1" s="17" thickBot="1">
+      <c r="B38" s="55" t="inlineStr">
+        <is>
+          <t>합계금액</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (A)+(B)+(C)</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="n"/>
+      <c r="E38" s="195" t="n"/>
+      <c r="F38" s="36" t="n"/>
+      <c r="G38" s="36" t="n"/>
+      <c r="H38" s="196">
         <f>H22+H36+H37</f>
-        <v>299389600</v>
-      </c>
-      <c r="I38" s="46">
+        <v/>
+      </c>
+      <c r="I38" s="196">
         <f>I22+I36+I37</f>
-        <v>250580000</v>
-      </c>
-      <c r="J38" s="46">
+        <v/>
+      </c>
+      <c r="J38" s="196">
         <f>J22+J36+J37</f>
-        <v>250580000</v>
-      </c>
-      <c r="K38" s="73"/>
-    </row>
-    <row r="39" spans="2:13" s="61" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="64" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="65"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="68">
+        <v/>
+      </c>
+      <c r="K38" s="73" t="n"/>
+    </row>
+    <row r="39" ht="23.25" customFormat="1" customHeight="1" s="61" thickBot="1">
+      <c r="B39" s="63" t="inlineStr">
+        <is>
+          <t>청구금액</t>
+        </is>
+      </c>
+      <c r="C39" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (VAT 포함)</t>
+        </is>
+      </c>
+      <c r="D39" s="65" t="n"/>
+      <c r="E39" s="197" t="n"/>
+      <c r="F39" s="67" t="n"/>
+      <c r="G39" s="67" t="n"/>
+      <c r="H39" s="198">
         <f>H38*1.1</f>
-        <v>329328560</v>
-      </c>
-      <c r="I39" s="68">
+        <v/>
+      </c>
+      <c r="I39" s="198">
         <f>I38*1.1</f>
-        <v>275638000</v>
-      </c>
-      <c r="J39" s="68">
+        <v/>
+      </c>
+      <c r="J39" s="198">
         <f>J38*1.1</f>
-        <v>275638000</v>
-      </c>
-      <c r="K39" s="69"/>
-      <c r="M39" s="62" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="106"/>
-      <c r="C40" s="106"/>
-      <c r="D40" s="106"/>
-      <c r="E40" s="106"/>
-      <c r="F40" s="106"/>
-      <c r="G40" s="106"/>
-      <c r="H40" s="106"/>
-      <c r="I40" s="106"/>
-      <c r="J40" s="106"/>
-      <c r="K40" s="106"/>
-      <c r="M40" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H41" s="27"/>
-      <c r="I41" s="80"/>
-      <c r="J41" s="80"/>
-      <c r="K41" s="26"/>
-      <c r="M41" s="31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H42" s="24"/>
-    </row>
-    <row r="44" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-    </row>
-    <row r="45" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-    </row>
-    <row r="47" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D47" s="30"/>
-      <c r="G47" s="29"/>
-    </row>
-    <row r="52" spans="5:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E52" s="24"/>
+        <v/>
+      </c>
+      <c r="K39" s="69" t="n"/>
+      <c r="M39" s="199" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" s="156">
+      <c r="B40" s="106" t="n"/>
+      <c r="C40" s="200" t="n"/>
+      <c r="D40" s="200" t="n"/>
+      <c r="E40" s="200" t="n"/>
+      <c r="F40" s="200" t="n"/>
+      <c r="G40" s="200" t="n"/>
+      <c r="H40" s="200" t="n"/>
+      <c r="I40" s="200" t="n"/>
+      <c r="J40" s="200" t="n"/>
+      <c r="K40" s="200" t="n"/>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1" s="156">
+      <c r="H41" s="201" t="n"/>
+      <c r="I41" s="202" t="n"/>
+      <c r="J41" s="202" t="n"/>
+      <c r="K41" s="203" t="n"/>
+      <c r="M41" s="204" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1" s="156">
+      <c r="H42" s="205" t="n"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="14.25" customHeight="1" s="156">
+      <c r="H44" s="205" t="n"/>
+      <c r="I44" s="205" t="n"/>
+      <c r="J44" s="205" t="n"/>
+    </row>
+    <row r="45" ht="14.25" customHeight="1" s="156">
+      <c r="I45" s="206" t="n"/>
+      <c r="J45" s="206" t="n"/>
+    </row>
+    <row r="46"/>
+    <row r="47" ht="14.25" customHeight="1" s="156">
+      <c r="D47" s="30" t="n"/>
+      <c r="G47" s="207" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52" ht="14.25" customHeight="1" s="156">
+      <c r="E52" s="205" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="B23:B31"/>
-    <mergeCell ref="C26:C31"/>
-    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="B40:K40"/>
     <mergeCell ref="K16:K21"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="F16:F20"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B14:K14"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:G7"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="C26:C31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="I6:K6"/>
+    <mergeCell ref="E3:G7"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="B14:K14"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="I7:K7"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.35433070866141736" bottom="0.2" header="0.19685039370078741" footer="0.23"/>
-  <pageSetup paperSize="8" orientation="landscape" verticalDpi="200" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.1574803149606299" right="0.1574803149606299" top="0.3543307086614174" bottom="0.2" header="0.1968503937007874" footer="0.23"/>
+  <pageSetup orientation="landscape" paperSize="8" verticalDpi="200"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>